--- a/Excel/PillConfig3.xlsx
+++ b/Excel/PillConfig3.xlsx
@@ -1254,7 +1254,7 @@
         <v>8</v>
       </c>
       <c r="G6" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H6" s="1">
         <v>10</v>
@@ -1277,7 +1277,7 @@
         <v>7</v>
       </c>
       <c r="G7" s="1">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H7" s="1">
         <v>10</v>
@@ -1300,7 +1300,7 @@
         <v>12</v>
       </c>
       <c r="G8" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H8" s="1">
         <v>10</v>
@@ -1323,7 +1323,7 @@
         <v>13</v>
       </c>
       <c r="G9" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H9" s="1">
         <v>10</v>
@@ -1369,7 +1369,7 @@
         <v>20</v>
       </c>
       <c r="G11" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H11" s="1">
         <v>10</v>
@@ -1392,7 +1392,7 @@
         <v>18</v>
       </c>
       <c r="G12" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H12" s="1">
         <v>10</v>
@@ -1415,7 +1415,7 @@
         <v>19</v>
       </c>
       <c r="G13" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H13" s="1">
         <v>10</v>
@@ -1438,7 +1438,7 @@
         <v>24</v>
       </c>
       <c r="G14" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H14" s="1">
         <v>10</v>
@@ -1483,10 +1483,10 @@
         <v>100</v>
       </c>
       <c r="F17" s="2">
-        <v>2002</v>
+        <v>2013</v>
       </c>
       <c r="G17" s="1">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H17" s="1">
         <v>30</v>

--- a/Excel/PillConfig3.xlsx
+++ b/Excel/PillConfig3.xlsx
@@ -123,7 +123,7 @@
     <t>生命倍率</t>
   </si>
   <si>
-    <t>防御倍率</t>
+    <t>破韧倍率</t>
   </si>
   <si>
     <t>韧性倍率</t>
@@ -1636,10 +1636,10 @@
         <v>700</v>
       </c>
       <c r="F23" s="2">
-        <v>2002</v>
+        <v>2013</v>
       </c>
       <c r="G23" s="1">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H23" s="1">
         <v>30</v>
@@ -1804,10 +1804,10 @@
         <v>1300</v>
       </c>
       <c r="F29" s="2">
-        <v>2002</v>
+        <v>2013</v>
       </c>
       <c r="G29" s="1">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H29" s="1">
         <v>30</v>

--- a/Excel/PillConfig3.xlsx
+++ b/Excel/PillConfig3.xlsx
@@ -333,12 +333,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1346,7 +1346,7 @@
         <v>9</v>
       </c>
       <c r="G10" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H10" s="1">
         <v>10</v>
